--- a/config/yunying/bao_zongzi_recipe.xlsx
+++ b/config/yunying/bao_zongzi_recipe.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12375" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="bao_zongzi_recipe" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="bao_zongzi_recipe" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="F4" s="1" t="inlineStr">
         <is>
-          <t>(金木犀風味のちまき)</t>
+          <t>（丹桂风味粽子）</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="F5" s="1" t="inlineStr">
         <is>
-          <t>(卵の黄身が入ったちまき)</t>
+          <t>（有蛋黄的粽子）</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="F6" s="1" t="inlineStr">
         <is>
-          <t>(栗の甘さがするちまき)</t>
+          <t>（栗子甜粽子）</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="F7" s="1" t="inlineStr">
         <is>
-          <t>(肉と金木犀の味)</t>
+          <t>（肉和丹桂的味道）</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1435,11 +1435,6 @@
           <t>{6360=1}</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1467,11 +1462,6 @@
           <t>{6361=1}</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1501,7 +1491,7 @@
       </c>
       <c r="F10" s="1" t="inlineStr">
         <is>
-          <t>(ナツメと卵の味)</t>
+          <t>（枣和鸡蛋的味道）</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1551,11 +1541,6 @@
           <t>{6362=1}</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1583,24 +1568,8 @@
           <t>{6363=1}</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
@@ -1629,7 +1598,7 @@
       </c>
       <c r="F14" s="1" t="inlineStr">
         <is>
-          <t>(金木犀風味のちまき)</t>
+          <t>（丹桂风味粽子）</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1681,7 +1650,7 @@
       </c>
       <c r="F15" s="1" t="inlineStr">
         <is>
-          <t>(卵の黄身が入ったちまき)</t>
+          <t>（有蛋黄的粽子）</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1733,7 +1702,7 @@
       </c>
       <c r="F16" s="1" t="inlineStr">
         <is>
-          <t>(栗の甘さがするちまき)</t>
+          <t>（栗子甜粽子）</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1785,7 +1754,7 @@
       </c>
       <c r="F17" s="1" t="inlineStr">
         <is>
-          <t>(肉と金木犀の味)</t>
+          <t>（肉和丹桂的味道）</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1835,11 +1804,6 @@
           <t>{6360=1}</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1867,11 +1831,6 @@
           <t>{6361=1}</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1901,7 +1860,7 @@
       </c>
       <c r="F20" s="1" t="inlineStr">
         <is>
-          <t>(ナツメと卵の味)</t>
+          <t>（枣和鸡蛋的味道）</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1951,11 +1910,6 @@
           <t>{6362=1}</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1983,11 +1937,6 @@
           <t>{6363=1}</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
